--- a/EXCEL/Data/køn_overenskomst.xlsx
+++ b/EXCEL/Data/køn_overenskomst.xlsx
@@ -76,7 +76,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 12.57.15</t>
+    <t>Kørsel 8.4.2026 13.56.24</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
